--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_freq_synth/CPL.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_freq_synth/CPL.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Clocks_Freq_Synth_board_mnt." localSheetId="0">Feuil1!$A$2:$G$175</definedName>
+    <definedName name="Clocks_Freq_Synth_board" localSheetId="0">Feuil1!$A$2:$E$175</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -20,8 +20,8 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="Clocks_Freq_Synth_board_mnt" type="6" refreshedVersion="3" background="1" saveData="1">
-    <textPr codePage="932" sourceFile="C:\Users\dell\Desktop\CrowdSupply\RADAR_V6\4_Schematics and Boards Layout\4_6_Schematics\FrequencySynthesizerBoard\Gerber_freq_synth\Clocks_Freq_Synth_board_mnt." decimal="," thousands=" " space="1" consecutive="1">
+  <connection id="1" name="Clocks_Freq_Synth_board" type="6" refreshedVersion="3" background="1" saveData="1">
+    <textPr codePage="932" sourceFile="C:\Users\dell\Desktop\CrowdSupply\RADAR_V6\4_Schematics and Boards Layout\4_6_Schematics\FrequencySynthesizerBoard\Clocks_Freq_Synth_board.mnt" decimal="," thousands=" " space="1" consecutive="1">
       <textFields count="6">
         <textField/>
         <textField/>
@@ -1472,22 +1472,22 @@
     <t>19.97</t>
   </si>
   <si>
-    <t>DESIGNATOR</t>
-  </si>
-  <si>
-    <t>Mid_X(mm)</t>
-  </si>
-  <si>
-    <t>Mid_Y(mm)</t>
-  </si>
-  <si>
-    <t>LAYER</t>
-  </si>
-  <si>
-    <t>ROTATION</t>
-  </si>
-  <si>
-    <t>TOP</t>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>Mid X (mm)</t>
+  </si>
+  <si>
+    <t>Mid Y (mm)</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>Rotation</t>
+  </si>
+  <si>
+    <t>Top</t>
   </si>
 </sst>
 </file>
@@ -1535,7 +1535,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Clocks_Freq_Synth_board_mnt." connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Clocks_Freq_Synth_board" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1826,13 +1826,11 @@
   <dimension ref="A1:E175"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
